--- a/public/plantillas/Makro/offer_template IT.xlsx
+++ b/public/plantillas/Makro/offer_template IT.xlsx
@@ -1042,25 +1042,404 @@
       </c>
     </row>
     <row r="12">
-      <c r="G12" s="5"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641312</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F12" s="0">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>106.56</v>
+      </c>
+      <c r="H12" s="0">
+        <v>2</v>
+      </c>
+      <c r="I12" s="0">
+        <v>3</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N12" s="0">
+        <v>104</v>
+      </c>
+      <c r="O12" s="0">
+        <v>102</v>
+      </c>
+      <c r="P12" s="0">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="0">
+        <v>98</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="G13" s="5"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641336</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F13" s="0">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>106.56</v>
+      </c>
+      <c r="H13" s="0">
+        <v>2</v>
+      </c>
+      <c r="I13" s="0">
+        <v>3</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N13" s="0">
+        <v>104</v>
+      </c>
+      <c r="O13" s="0">
+        <v>102</v>
+      </c>
+      <c r="P13" s="0">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="0">
+        <v>98</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENVIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641329</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F14" s="0">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>106.56</v>
+      </c>
+      <c r="H14" s="0">
+        <v>2</v>
+      </c>
+      <c r="I14" s="0">
+        <v>3</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N14" s="0">
+        <v>104</v>
+      </c>
+      <c r="O14" s="0">
+        <v>102</v>
+      </c>
+      <c r="P14" s="0">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="0">
+        <v>98</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15.5">
-      <c r="G15" s="4"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641343</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F15" s="0">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>106.56</v>
+      </c>
+      <c r="H15" s="0">
+        <v>2</v>
+      </c>
+      <c r="I15" s="0">
+        <v>3</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N15" s="0">
+        <v>104</v>
+      </c>
+      <c r="O15" s="0">
+        <v>102</v>
+      </c>
+      <c r="P15" s="0">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="0">
+        <v>98</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15.5">
-      <c r="G16" s="4"/>
+      <c r="A16" s="3">
+        <v>8437027641350</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F16" s="0">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>142.62</v>
+      </c>
+      <c r="H16" s="0">
+        <v>2</v>
+      </c>
+      <c r="I16" s="0">
+        <v>3</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N16" s="0">
+        <v>140</v>
+      </c>
+      <c r="O16" s="0">
+        <v>138</v>
+      </c>
+      <c r="P16" s="0">
+        <v>136</v>
+      </c>
+      <c r="Q16" s="0">
+        <v>134</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15.5">
-      <c r="G17" s="4"/>
+      <c r="A17" s="3">
+        <v>8437027641374</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F17" s="0">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>142.62</v>
+      </c>
+      <c r="H17" s="0">
+        <v>2</v>
+      </c>
+      <c r="I17" s="0">
+        <v>3</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N17" s="0">
+        <v>140</v>
+      </c>
+      <c r="O17" s="0">
+        <v>138</v>
+      </c>
+      <c r="P17" s="0">
+        <v>136</v>
+      </c>
+      <c r="Q17" s="0">
+        <v>134</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15.5">
-      <c r="G18" s="4"/>
+      <c r="A18" s="3">
+        <v>8437027641367</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F18" s="0">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>142.62</v>
+      </c>
+      <c r="H18" s="0">
+        <v>2</v>
+      </c>
+      <c r="I18" s="0">
+        <v>3</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N18" s="0">
+        <v>140</v>
+      </c>
+      <c r="O18" s="0">
+        <v>138</v>
+      </c>
+      <c r="P18" s="0">
+        <v>136</v>
+      </c>
+      <c r="Q18" s="0">
+        <v>134</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15.5">
-      <c r="G19" s="4"/>
+      <c r="A19" s="3">
+        <v>8437027641381</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F19" s="0">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>142.62</v>
+      </c>
+      <c r="H19" s="0">
+        <v>2</v>
+      </c>
+      <c r="I19" s="0">
+        <v>3</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N19" s="0">
+        <v>140</v>
+      </c>
+      <c r="O19" s="0">
+        <v>138</v>
+      </c>
+      <c r="P19" s="0">
+        <v>136</v>
+      </c>
+      <c r="Q19" s="0">
+        <v>134</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15.5">
       <c r="G20" s="4"/>

--- a/public/plantillas/Makro/offer_template IT.xlsx
+++ b/public/plantillas/Makro/offer_template IT.xlsx
@@ -1442,34 +1442,514 @@
       </c>
     </row>
     <row r="20" ht="15.5">
-      <c r="G20" s="4"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641534</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F20" s="0">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>98.36</v>
+      </c>
+      <c r="H20" s="0">
+        <v>2</v>
+      </c>
+      <c r="I20" s="0">
+        <v>3</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N20" s="0">
+        <v>95.41</v>
+      </c>
+      <c r="O20" s="0">
+        <v>94.43</v>
+      </c>
+      <c r="P20" s="0">
+        <v>93.44</v>
+      </c>
+      <c r="Q20" s="0">
+        <v>92.46</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15.5">
-      <c r="G21" s="4"/>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641480</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F21" s="0">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>97.54</v>
+      </c>
+      <c r="H21" s="0">
+        <v>2</v>
+      </c>
+      <c r="I21" s="0">
+        <v>3</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N21" s="0">
+        <v>94.61</v>
+      </c>
+      <c r="O21" s="0">
+        <v>93.64</v>
+      </c>
+      <c r="P21" s="0">
+        <v>92.66</v>
+      </c>
+      <c r="Q21" s="0">
+        <v>91.69</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15.5">
-      <c r="G22" s="4"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641497</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F22" s="0">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>245.9</v>
+      </c>
+      <c r="H22" s="0">
+        <v>2</v>
+      </c>
+      <c r="I22" s="0">
+        <v>3</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N22" s="0">
+        <v>238.52</v>
+      </c>
+      <c r="O22" s="0">
+        <v>236.06</v>
+      </c>
+      <c r="P22" s="0">
+        <v>233.61</v>
+      </c>
+      <c r="Q22" s="0">
+        <v>231.15</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15.5">
-      <c r="G23" s="4"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641442</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F23" s="0">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>245.9</v>
+      </c>
+      <c r="H23" s="0">
+        <v>2</v>
+      </c>
+      <c r="I23" s="0">
+        <v>3</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N23" s="0">
+        <v>238.52</v>
+      </c>
+      <c r="O23" s="0">
+        <v>236.06</v>
+      </c>
+      <c r="P23" s="0">
+        <v>233.61</v>
+      </c>
+      <c r="Q23" s="0">
+        <v>231.15</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15.5">
-      <c r="G24" s="4"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641503</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F24" s="0">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>146.72</v>
+      </c>
+      <c r="H24" s="0">
+        <v>2</v>
+      </c>
+      <c r="I24" s="0">
+        <v>3</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N24" s="0">
+        <v>142.32</v>
+      </c>
+      <c r="O24" s="0">
+        <v>140.85</v>
+      </c>
+      <c r="P24" s="0">
+        <v>139.38</v>
+      </c>
+      <c r="Q24" s="0">
+        <v>137.92</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15.5">
-      <c r="G25" s="4"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641459</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F25" s="0">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>146.72</v>
+      </c>
+      <c r="H25" s="0">
+        <v>2</v>
+      </c>
+      <c r="I25" s="0">
+        <v>3</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N25" s="0">
+        <v>142.32</v>
+      </c>
+      <c r="O25" s="0">
+        <v>140.85</v>
+      </c>
+      <c r="P25" s="0">
+        <v>139.38</v>
+      </c>
+      <c r="Q25" s="0">
+        <v>137.92</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.5">
-      <c r="G26" s="4"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641510</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F26" s="0">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>163.11</v>
+      </c>
+      <c r="H26" s="0">
+        <v>2</v>
+      </c>
+      <c r="I26" s="0">
+        <v>3</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N26" s="0">
+        <v>158.22</v>
+      </c>
+      <c r="O26" s="0">
+        <v>156.59</v>
+      </c>
+      <c r="P26" s="0">
+        <v>154.95</v>
+      </c>
+      <c r="Q26" s="0">
+        <v>153.32</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.5">
-      <c r="G27" s="4"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641466</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F27" s="0">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>163.93</v>
+      </c>
+      <c r="H27" s="0">
+        <v>2</v>
+      </c>
+      <c r="I27" s="0">
+        <v>3</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N27" s="0">
+        <v>159.01</v>
+      </c>
+      <c r="O27" s="0">
+        <v>157.37</v>
+      </c>
+      <c r="P27" s="0">
+        <v>155.73</v>
+      </c>
+      <c r="Q27" s="0">
+        <v>154.09</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15.5">
-      <c r="G28" s="4"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641527</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F28" s="0">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4">
+        <v>228.69</v>
+      </c>
+      <c r="H28" s="0">
+        <v>2</v>
+      </c>
+      <c r="I28" s="0">
+        <v>3</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N28" s="0">
+        <v>221.83</v>
+      </c>
+      <c r="O28" s="0">
+        <v>219.54</v>
+      </c>
+      <c r="P28" s="0">
+        <v>217.26</v>
+      </c>
+      <c r="Q28" s="0">
+        <v>214.97</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.5">
-      <c r="G29" s="4"/>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641473</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F29" s="0">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4">
+        <v>228.69</v>
+      </c>
+      <c r="H29" s="0">
+        <v>2</v>
+      </c>
+      <c r="I29" s="0">
+        <v>3</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT_MAIN</t>
+        </is>
+      </c>
+      <c r="N29" s="0">
+        <v>221.83</v>
+      </c>
+      <c r="O29" s="0">
+        <v>219.54</v>
+      </c>
+      <c r="P29" s="0">
+        <v>217.26</v>
+      </c>
+      <c r="Q29" s="0">
+        <v>214.97</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.5">
       <c r="G30" s="4"/>
